--- a/generated/spreadsheet/listed-building-consent-lbc.xlsx
+++ b/generated/spreadsheet/listed-building-consent-lbc.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -568,14 +568,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -599,19 +599,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -630,19 +630,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -661,14 +661,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -697,13 +701,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -732,13 +736,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -767,23 +771,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -802,18 +806,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -837,23 +841,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -877,12 +885,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -916,12 +924,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -931,7 +939,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -955,17 +963,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -984,22 +992,18 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1009,7 +1013,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1032,13 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1063,48 +1067,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1114,32 +1118,28 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1163,14 +1163,18 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1180,7 +1184,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1199,18 +1203,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1220,51 +1224,47 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1272,14 +1272,18 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1308,13 +1312,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1324,7 +1328,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1343,13 +1347,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1378,13 +1382,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1413,13 +1417,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1429,7 +1433,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1443,18 +1447,14 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,19 +1478,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1500,58 +1500,58 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1575,14 +1575,18 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1592,7 +1596,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1611,18 +1615,18 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1632,51 +1636,47 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1684,14 +1684,18 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1701,7 +1705,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1720,13 +1724,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1736,7 +1740,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1755,13 +1759,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1790,13 +1794,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1825,13 +1829,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1841,32 +1845,32 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -1876,24 +1880,24 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Community consultation</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1901,12 +1905,12 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1916,19 +1920,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Community consultation</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>What community consultation activities have taken place as part of the application</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Have consulted</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1936,26 +1932,34 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Whether community consultation has been carried out</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1963,34 +1967,26 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1998,17 +1994,17 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2013,7 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2025,7 +2021,7 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2040,11 +2036,19 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2052,7 +2056,7 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2062,24 +2066,16 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2087,12 +2083,12 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2106,7 +2102,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2114,12 +2110,12 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2129,11 +2125,19 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Demolition</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Is propsing demolition</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2141,12 +2145,12 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Does the proposal include partial or total demolition of a listed building?</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2156,19 +2160,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Demolition</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Is propsing demolition</t>
+          <t>Is total demolition</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2176,7 +2172,7 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include partial or total demolition of a listed building?</t>
+          <t>Indicating whether the proposal involves total demolition of a listed building</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2186,7 +2182,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2191,7 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Is total demolition</t>
+          <t>Demolition building in curtilage</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2203,7 +2199,7 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Indicating whether the proposal involves total demolition of a listed building</t>
+          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2222,7 +2218,7 @@
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Demolition building in curtilage</t>
+          <t>Demolition part</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2230,7 +2226,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
+          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2249,7 +2245,7 @@
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Demolition part</t>
+          <t>Listed building volume</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -2257,12 +2253,12 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
+          <t>Volume of listed building in cubic metres</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2276,7 +2272,7 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Listed building volume</t>
+          <t>Demolition volume</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -2284,7 +2280,7 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Volume of listed building in cubic metres</t>
+          <t>Volume of part to be demolished in cubic metres</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2303,7 +2299,7 @@
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Demolition volume</t>
+          <t>Part built date</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2311,12 +2307,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Volume of part to be demolished in cubic metres</t>
+          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2330,7 +2326,7 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Part built date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2338,17 +2334,17 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
+          <t>Description of the building or part you are proposing to demolish</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2353,7 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2365,7 +2361,7 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Description of the building or part you are proposing to demolish</t>
+          <t>Reason for demolition</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2380,11 +2376,19 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Immunity from listing</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Certificate of immunity sought</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2392,12 +2396,12 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Reason for demolition</t>
+          <t>Has a certificate of immunity been sought</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2407,19 +2411,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Immunity from listing</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Certificate of immunity sought</t>
+          <t>Application result</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2427,26 +2423,34 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Has a certificate of immunity been sought</t>
+          <t>Provide the result of the application for a certificate of immunity</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Listed building alterations</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes being made to a listed building as part of development works</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Application result</t>
+          <t>Proposal alter listed building</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2454,34 +2458,26 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Provide the result of the application for a certificate of immunity</t>
+          <t>True or False if proposal includes alterations to a listed building</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Listed building alterations</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes being made to a listed building as part of development works</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Proposal alter listed building</t>
+          <t>Proposal alteration types[]</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2489,17 +2485,17 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>True or False if proposal includes alterations to a listed building</t>
+          <t>Select from a list of listed building alteration types, select all that apply</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2508,51 +2504,59 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Proposal alteration types[]</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
+          <t>Document reference[]</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Select from a list of listed building alteration types, select all that apply</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Listed building grade</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>The grade of any listed building affected by the proposed development.</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Document reference[]</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Listed building grade</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2562,19 +2566,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>The grade of any listed building affected by the proposed development.</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Listed building grade</t>
+          <t>Listed building</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2582,17 +2578,17 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
+          <t>Listed building reference for cross-referencing with listed building records</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2597,7 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Listed building</t>
+          <t>Provided by</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2609,12 +2605,12 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Listed building reference for cross-referencing with listed building records</t>
+          <t>Source of the listed building grade information</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2624,19 +2620,31 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Building element type</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Source of the listed building grade information</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2646,21 +2654,13 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Building elements[]</t>
@@ -2668,24 +2668,24 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Building element type</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2699,14 +2699,14 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -2730,19 +2730,19 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Materials not applicable</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Indicates this building element is not relevant to the application</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -2761,14 +2761,14 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -2787,19 +2787,15 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Materials not known</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -2809,7 +2805,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2818,20 +2814,24 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2841,28 +2841,32 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n"/>
-      <c r="B74" s="2" t="n"/>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -2872,37 +2876,37 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr"/>
+          <t>Owners of listed building[]</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2921,13 +2925,13 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -2937,7 +2941,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2956,13 +2960,13 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -2991,13 +2995,13 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3026,13 +3030,13 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3042,7 +3046,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3056,23 +3060,19 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3086,24 +3086,20 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Owners of listed building[]</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3117,15 +3113,19 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3149,19 +3149,19 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -3175,29 +3175,25 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3202,7 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3214,12 +3210,12 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -3233,7 +3229,7 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3241,7 +3237,7 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -3260,7 +3256,7 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3268,7 +3264,7 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -3283,11 +3279,19 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="2" t="n"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -3295,34 +3299,26 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -3330,17 +3326,17 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3345,7 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3357,7 +3353,7 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -3376,7 +3372,7 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3384,7 +3380,7 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -3403,7 +3399,7 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3411,7 +3407,7 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -3426,11 +3422,19 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n"/>
-      <c r="B93" s="2" t="n"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3438,7 +3442,7 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -3448,24 +3452,16 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -3473,12 +3469,12 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -3492,7 +3488,7 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -3500,17 +3496,17 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3515,7 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -3527,17 +3523,17 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3542,7 @@
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -3554,26 +3550,34 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="2" t="n"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Details of any other development proposals made for the site</t>
+        </is>
+      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Has related applications</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -3581,47 +3585,43 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Details of any other development proposals made for the site</t>
-        </is>
-      </c>
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr"/>
+          <t>Related applications[]</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -3640,14 +3640,14 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -3671,14 +3671,14 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -3688,33 +3688,41 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="2" t="n"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -3724,16 +3732,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -3741,19 +3741,19 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -3772,14 +3772,14 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3803,19 +3803,19 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -3834,14 +3834,14 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -3865,14 +3865,14 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -3896,14 +3896,14 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -3927,19 +3927,19 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -3958,14 +3958,14 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -3980,50 +3980,46 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n"/>
-      <c r="B111" s="2" t="n"/>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
@@ -4031,12 +4027,12 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -4050,7 +4046,7 @@
       <c r="B113" s="2" t="n"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
@@ -4058,17 +4054,17 @@
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4077,15 +4073,19 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4109,14 +4109,14 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -4140,14 +4140,14 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -4156,37 +4156,6 @@
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n"/>
-      <c r="B117" s="2" t="n"/>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr"/>
-      <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -4194,46 +4163,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A103:A111"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B68:B74"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B103:B111"/>
-    <mergeCell ref="B75:B88"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B89:B93"/>
-    <mergeCell ref="B94:B98"/>
-    <mergeCell ref="A68:A74"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B51:B59"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="A94:A98"/>
-    <mergeCell ref="A112:A117"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A75:A88"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="B112:B117"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A51:A59"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A42"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A89:A93"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="B88:B92"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="A50:A58"/>
+    <mergeCell ref="B74:B87"/>
+    <mergeCell ref="A111:A116"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B41"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B111:B116"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="A93:A97"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A88:A92"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="A102:A110"/>
+    <mergeCell ref="A41"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B50:B58"/>
+    <mergeCell ref="B93:B97"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A74:A87"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="B102:B110"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="B67:B73"/>
+    <mergeCell ref="A98:A101"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/listed-building-consent-lbc.xlsx
+++ b/generated/spreadsheet/listed-building-consent-lbc.xlsx
@@ -3683,7 +3683,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">

--- a/generated/spreadsheet/listed-building-consent-lbc.xlsx
+++ b/generated/spreadsheet/listed-building-consent-lbc.xlsx
@@ -2115,7 +2115,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">

--- a/generated/spreadsheet/listed-building-consent-lbc.xlsx
+++ b/generated/spreadsheet/listed-building-consent-lbc.xlsx
@@ -433,7 +433,7 @@
     <col width="58" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
@@ -2632,24 +2632,20 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -2668,24 +2664,24 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2699,14 +2695,14 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -2730,19 +2726,19 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">

--- a/generated/spreadsheet/listed-building-consent-lbc.xlsx
+++ b/generated/spreadsheet/listed-building-consent-lbc.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -491,29 +491,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -563,19 +563,19 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -594,24 +594,24 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -625,24 +625,24 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -656,28 +656,24 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -691,7 +687,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -701,13 +697,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -736,13 +732,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -761,7 +757,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -771,23 +767,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -796,7 +792,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -806,18 +802,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -831,7 +827,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -841,27 +837,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -870,7 +862,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -900,7 +892,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -909,7 +901,7 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -924,12 +916,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -939,7 +931,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -948,7 +940,7 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -963,17 +955,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -987,33 +979,37 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1032,18 +1028,18 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1057,7 +1053,7 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1067,48 +1063,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1118,28 +1114,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1163,18 +1163,14 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1184,7 +1180,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1203,18 +1199,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1224,47 +1220,51 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1272,18 +1272,14 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1312,13 +1308,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1328,7 +1324,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1347,13 +1343,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1382,13 +1378,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1417,13 +1413,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1433,7 +1429,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1447,14 +1443,18 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,19 +1478,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1500,58 +1500,58 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1575,18 +1575,14 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1596,7 +1592,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1615,18 +1611,18 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1636,47 +1632,51 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1684,18 +1684,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1705,7 +1701,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1724,13 +1720,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1740,7 +1736,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1759,13 +1755,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1794,13 +1790,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1829,13 +1825,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1845,32 +1841,32 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -1880,24 +1876,24 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Community consultation</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>What community consultation activities have taken place as part of the application</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Have consulted</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1905,12 +1901,12 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Whether community consultation has been carried out</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1920,11 +1916,19 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Community consultation</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>What community consultation activities have taken place as part of the application</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1932,34 +1936,26 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1967,26 +1963,34 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1994,17 +1998,17 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2017,7 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2021,7 +2025,7 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2036,19 +2040,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2056,7 +2052,7 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2066,16 +2062,24 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2083,12 +2087,12 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2102,7 +2106,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2110,12 +2114,12 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2125,19 +2129,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Demolition</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Is propsing demolition</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2145,12 +2141,12 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include partial or total demolition of a listed building?</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2160,11 +2156,19 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Demolition</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Is total demolition</t>
+          <t>Is propsing demolition</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2172,7 +2176,7 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Indicating whether the proposal involves total demolition of a listed building</t>
+          <t>Does the proposal include partial or total demolition of a listed building?</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2182,7 +2186,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2195,7 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Demolition building in curtilage</t>
+          <t>Is total demolition</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2199,7 +2203,7 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
+          <t>Indicating whether the proposal involves total demolition of a listed building</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2218,7 +2222,7 @@
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Demolition part</t>
+          <t>Demolition building in curtilage</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2226,7 +2230,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
+          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2245,7 +2249,7 @@
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Listed building volume</t>
+          <t>Demolition part</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -2253,12 +2257,12 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Volume of listed building in cubic metres</t>
+          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2272,7 +2276,7 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Demolition volume</t>
+          <t>Listed building volume</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -2280,12 +2284,12 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Volume of part to be demolished in cubic metres</t>
+          <t>Volume of listed building in cubic metres</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2299,7 +2303,7 @@
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Part built date</t>
+          <t>Demolition volume</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2307,12 +2311,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
+          <t>Volume of part to be demolished in cubic metres</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2326,7 +2330,7 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Part built date</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2334,17 +2338,17 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Description of the building or part you are proposing to demolish</t>
+          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2357,7 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2361,7 +2365,7 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Reason for demolition</t>
+          <t>Description of the building or part you are proposing to demolish</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2376,19 +2380,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Immunity from listing</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Certificate of immunity sought</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2396,12 +2392,12 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Has a certificate of immunity been sought</t>
+          <t>Reason for demolition</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2411,11 +2407,19 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="n"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Immunity from listing</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Application result</t>
+          <t>Certificate of immunity sought</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2423,34 +2427,26 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Provide the result of the application for a certificate of immunity</t>
+          <t>Has a certificate of immunity been sought</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Listed building alterations</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes being made to a listed building as part of development works</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Proposal alter listed building</t>
+          <t>Application result</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2458,26 +2454,34 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>True or False if proposal includes alterations to a listed building</t>
+          <t>Provide the result of the application for a certificate of immunity</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Listed building alterations</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes being made to a listed building as part of development works</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Proposal alteration types[]</t>
+          <t>Proposal alter listed building</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2485,17 +2489,17 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Select from a list of listed building alteration types, select all that apply</t>
+          <t>True or False if proposal includes alterations to a listed building</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2504,59 +2508,51 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Document reference[]</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Proposal alteration types[]</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Select from a list of listed building alteration types, select all that apply</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>The grade of any listed building affected by the proposed development.</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
+          <t>Document reference[]</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2566,11 +2562,19 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Listed building grade</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>The grade of any listed building affected by the proposed development.</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Listed building</t>
+          <t>Listed building grade</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2578,17 +2582,17 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Listed building reference for cross-referencing with listed building records</t>
+          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2601,7 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
+          <t>Listed building</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2605,12 +2609,12 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Source of the listed building grade information</t>
+          <t>Listed building reference for cross-referencing with listed building records</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2620,19 +2624,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
+          <t>Provided by</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2640,43 +2636,47 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Source of the listed building grade information</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -2695,24 +2695,24 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2726,14 +2726,14 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2757,19 +2757,19 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2783,15 +2783,19 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Materials not known</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -2801,7 +2805,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2810,24 +2814,20 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2837,32 +2837,28 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -2872,37 +2868,37 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="2" t="n"/>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Owners of listed building[]</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2921,13 +2917,13 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -2937,7 +2933,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2956,13 +2952,13 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -2991,13 +2987,13 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3026,13 +3022,13 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3042,7 +3038,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3056,19 +3052,23 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Notice date</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3082,20 +3082,24 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
+          <t>Owners of listed building[]</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3109,29 +3113,25 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Newspaper name</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3140,29 +3140,25 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3171,25 +3167,29 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3198,25 +3198,29 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3229,7 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3233,7 +3237,7 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -3243,7 +3247,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3256,7 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3260,34 +3264,26 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -3295,12 +3291,12 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -3310,11 +3306,19 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n"/>
-      <c r="B89" s="2" t="n"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -3322,17 +3326,17 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3345,7 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3349,7 +3353,7 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -3368,7 +3372,7 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3376,12 +3380,12 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -3395,7 +3399,7 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3403,12 +3407,12 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -3418,19 +3422,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3438,7 +3434,7 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -3448,16 +3444,24 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -3465,12 +3469,12 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -3484,7 +3488,7 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -3492,17 +3496,17 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3515,7 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -3519,17 +3523,17 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3542,7 @@
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -3546,34 +3550,26 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Details of any other development proposals made for the site</t>
-        </is>
-      </c>
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -3581,43 +3577,47 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n"/>
-      <c r="B99" s="2" t="n"/>
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Details of any other development proposals made for the site</t>
+        </is>
+      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Has related applications</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -3636,14 +3636,14 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -3667,58 +3667,50 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -3728,8 +3720,16 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="2" t="n"/>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -3737,19 +3737,19 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -3768,14 +3768,14 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3799,19 +3799,19 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -3830,19 +3830,19 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -3861,19 +3861,19 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -3892,19 +3892,19 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -3923,19 +3923,19 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -3954,14 +3954,14 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -3976,46 +3976,50 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n"/>
-      <c r="B112" s="2" t="n"/>
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
@@ -4023,12 +4027,12 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -4042,7 +4046,7 @@
       <c r="B113" s="2" t="n"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
@@ -4050,17 +4054,17 @@
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4069,19 +4073,15 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4105,14 +4105,14 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -4136,22 +4136,53 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -4159,46 +4190,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B35:B40"/>
-    <mergeCell ref="B88:B92"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="A50:A58"/>
-    <mergeCell ref="B74:B87"/>
-    <mergeCell ref="A111:A116"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B41"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B111:B116"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="A93:A97"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A88:A92"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="A102:A110"/>
-    <mergeCell ref="A41"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B50:B58"/>
-    <mergeCell ref="B93:B97"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A74:A87"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A23:A30"/>
-    <mergeCell ref="B102:B110"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="B67:B73"/>
-    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A103:A111"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="B68:B74"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B103:B111"/>
+    <mergeCell ref="B75:B88"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B89:B93"/>
+    <mergeCell ref="B94:B98"/>
+    <mergeCell ref="A68:A74"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B51:B59"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="B42"/>
+    <mergeCell ref="A94:A98"/>
+    <mergeCell ref="A112:A117"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A75:A88"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="B112:B117"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A51:A59"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="A42"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="A89:A93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/listed-building-consent-lbc.xlsx
+++ b/generated/spreadsheet/listed-building-consent-lbc.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -435,9 +435,9 @@
     <col width="43" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1413,13 +1413,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1448,13 +1452,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,14 +1486,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1509,19 +1525,19 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1531,58 +1547,58 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1606,18 +1622,14 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1627,7 +1639,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1646,18 +1658,18 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1667,47 +1679,51 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1715,18 +1731,14 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1736,7 +1748,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1755,13 +1767,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1771,7 +1783,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1790,13 +1802,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1825,13 +1837,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1860,102 +1872,122 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Checklist</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>List of the document types required for the given application type</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Community consultation</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>What community consultation activities have taken place as part of the application</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Have consulted</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Whether community consultation has been carried out</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1963,7 +1995,7 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1973,24 +2005,24 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Community consultation</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1998,7 +2030,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2017,7 +2049,7 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2025,7 +2057,7 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2040,11 +2072,19 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2052,31 +2092,23 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Person reference</t>
@@ -2087,7 +2119,7 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2097,7 +2129,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2138,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2114,26 +2146,34 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2141,12 +2181,12 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2156,19 +2196,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Demolition</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Is propsing demolition</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2176,7 +2208,7 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include partial or total demolition of a listed building?</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2195,7 +2227,7 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Is total demolition</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2203,26 +2235,34 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Indicating whether the proposal involves total demolition of a listed building</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Demolition</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Demolition building in curtilage</t>
+          <t>Is propsing demolition</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2230,7 +2270,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
+          <t>Does the proposal include partial or total demolition of a listed building?</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2240,7 +2280,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2289,7 @@
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Demolition part</t>
+          <t>Is total demolition</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -2257,7 +2297,7 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
+          <t>Indicating whether the proposal involves total demolition of a listed building</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2276,7 +2316,7 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Listed building volume</t>
+          <t>Demolition building in curtilage</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -2284,12 +2324,12 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Volume of listed building in cubic metres</t>
+          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2303,7 +2343,7 @@
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Demolition volume</t>
+          <t>Demolition part</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2311,12 +2351,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Volume of part to be demolished in cubic metres</t>
+          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2330,7 +2370,7 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Part built date</t>
+          <t>Listed building volume</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2338,12 +2378,12 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
+          <t>Volume of listed building in cubic metres</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2357,7 +2397,7 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Demolition volume</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2365,17 +2405,17 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Description of the building or part you are proposing to demolish</t>
+          <t>Volume of part to be demolished in cubic metres</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2424,7 @@
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Part built date</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2392,34 +2432,26 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Reason for demolition</t>
+          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Immunity from listing</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Certificate of immunity sought</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2427,12 +2459,12 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Has a certificate of immunity been sought</t>
+          <t>Description of the building or part you are proposing to demolish</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2446,7 +2478,7 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Application result</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2454,7 +2486,7 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Provide the result of the application for a certificate of immunity</t>
+          <t>Reason for demolition</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2464,24 +2496,24 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Listed building alterations</t>
+          <t>Immunity from listing</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes being made to a listed building as part of development works</t>
+          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Proposal alter listed building</t>
+          <t>Certificate of immunity sought</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2489,12 +2521,12 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>True or False if proposal includes alterations to a listed building</t>
+          <t>Has a certificate of immunity been sought</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2508,7 +2540,7 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Proposal alteration types[]</t>
+          <t>Application result</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -2516,12 +2548,12 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Select from a list of listed building alteration types, select all that apply</t>
+          <t>Provide the result of the application for a certificate of immunity</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2531,28 +2563,32 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Listed building alterations</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes being made to a listed building as part of development works</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Document reference[]</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Proposal alter listed building</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>True or False if proposal includes alterations to a listed building</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2562,19 +2598,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>The grade of any listed building affected by the proposed development.</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Listed building grade</t>
+          <t>Proposal alteration types[]</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2582,7 +2610,7 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
+          <t>Select from a list of listed building alteration types, select all that apply</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -2592,7 +2620,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2601,15 +2629,19 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Listed building</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+          <t>Document reference[]</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Listed building reference for cross-referencing with listed building records</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2619,16 +2651,24 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Listed building grade</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>The grade of any listed building affected by the proposed development.</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
+          <t>Listed building grade</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2636,7 +2676,7 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Source of the listed building grade information</t>
+          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2646,24 +2686,16 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
+          <t>Listed building</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2671,17 +2703,17 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Listed building reference for cross-referencing with listed building records</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2690,19 +2722,15 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Provided by</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Source of the listed building grade information</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -2712,38 +2740,42 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n"/>
-      <c r="B70" s="2" t="n"/>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Existing materials</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2757,24 +2789,24 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2788,19 +2820,19 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -2814,25 +2846,29 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Proposed materials</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2841,46 +2877,38 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Providing additional material information</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -2888,7 +2916,7 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -2907,23 +2935,19 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Owners of listed building[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -2933,37 +2957,37 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Owners of listed building[]</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -2987,13 +3011,13 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3003,7 +3027,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3022,13 +3046,13 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3057,13 +3081,13 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3073,7 +3097,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3087,24 +3111,32 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3113,20 +3145,32 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
+          <t>Owners of listed building[]</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -3140,15 +3184,27 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr"/>
+          <t>Owners of listed building[]</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -3167,29 +3223,29 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners of listed building[]</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3198,29 +3254,25 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3281,7 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3237,7 +3289,7 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -3247,7 +3299,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3256,20 +3308,24 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -3283,15 +3339,19 @@
       <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -3306,19 +3366,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -3326,12 +3378,12 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -3345,7 +3397,7 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3353,17 +3405,17 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3424,7 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3380,26 +3432,34 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="2" t="n"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3407,17 +3467,17 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3486,7 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3434,7 +3494,7 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -3449,19 +3509,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -3469,7 +3521,7 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -3479,7 +3531,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3540,7 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -3496,17 +3548,17 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3567,7 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -3523,12 +3575,12 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -3538,11 +3590,19 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="2" t="n"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -3550,12 +3610,12 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3569,7 +3629,7 @@
       <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -3577,34 +3637,26 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Details of any other development proposals made for the site</t>
-        </is>
-      </c>
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
@@ -3612,17 +3664,17 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3631,24 +3683,20 @@
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Proposal completed</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -3662,99 +3710,91 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="2" t="n"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Details of any other development proposals made for the site</t>
+        </is>
+      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Has related applications</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3763,19 +3803,19 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3785,7 +3825,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3794,24 +3834,24 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -3821,8 +3861,16 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="2" t="n"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -3830,24 +3878,24 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3861,24 +3909,28 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3892,19 +3944,23 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -3923,19 +3979,23 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -3954,14 +4014,18 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -3985,19 +4049,19 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -4007,37 +4071,33 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4046,25 +4106,29 @@
       <c r="B113" s="2" t="n"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4073,20 +4137,24 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -4096,28 +4164,32 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n"/>
-      <c r="B115" s="2" t="n"/>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -4131,24 +4203,20 @@
       <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -4162,27 +4230,116 @@
       <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n"/>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -4190,46 +4347,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A103:A111"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A49"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B68:B74"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B103:B111"/>
-    <mergeCell ref="B75:B88"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B89:B93"/>
-    <mergeCell ref="B94:B98"/>
-    <mergeCell ref="A68:A74"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B51:B59"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="B115:B120"/>
+    <mergeCell ref="A44"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="A97:A101"/>
+    <mergeCell ref="B53:B61"/>
+    <mergeCell ref="B92:B96"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="B77:B91"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A106:A114"/>
+    <mergeCell ref="A53:A61"/>
+    <mergeCell ref="B97:B101"/>
+    <mergeCell ref="A92:A96"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="A94:A98"/>
-    <mergeCell ref="A112:A117"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A75:A88"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="B112:B117"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A51:A59"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B106:B114"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="A70:A76"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="B44"/>
+    <mergeCell ref="B70:B76"/>
     <mergeCell ref="B20:B23"/>
+    <mergeCell ref="A77:A91"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A42"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A89:A93"/>
+    <mergeCell ref="A115:A120"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
